--- a/Reports/SA-55209-ShipTo-Terms-vs-FreightCode-2026-09-23.xlsx
+++ b/Reports/SA-55209-ShipTo-Terms-vs-FreightCode-2026-09-23.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF470FF9-E0E8-4C70-9F50-34EDCBFCA75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D23A483-0BC3-46E3-93C6-FBA7B7AFD054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShipTo Prepaid vs Terms" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ShipTo Prepaid vs Terms'!$A$1:$H$174</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="368">
   <si>
     <t>customer_id</t>
   </si>
@@ -1109,13 +1110,31 @@
   </si>
   <si>
     <t>Kailia Corp</t>
+  </si>
+  <si>
+    <t>Change TO</t>
+  </si>
+  <si>
+    <t>Out Freight</t>
+  </si>
+  <si>
+    <t>old_freight_code_uid</t>
+  </si>
+  <si>
+    <t>backed_up_at</t>
+  </si>
+  <si>
+    <t>backed_up_by</t>
+  </si>
+  <si>
+    <t>AHI\mgoldyn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1133,8 +1152,28 @@
       <sz val="11"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1145,6 +1184,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1160,7 +1211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1176,6 +1227,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1480,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:I174"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="6" customWidth="1"/>
@@ -1491,9 +1555,10 @@
     <col min="6" max="6" width="9" style="4" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1518,8 +1583,11 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1001535</v>
       </c>
@@ -1544,8 +1612,11 @@
       <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>1005000</v>
       </c>
@@ -1570,8 +1641,11 @@
       <c r="H3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1006513</v>
       </c>
@@ -1596,8 +1670,11 @@
       <c r="H4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1011370</v>
       </c>
@@ -1622,8 +1699,11 @@
       <c r="H5" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1013940</v>
       </c>
@@ -1648,8 +1728,11 @@
       <c r="H6" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1014465</v>
       </c>
@@ -1674,8 +1757,11 @@
       <c r="H7" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>1018585</v>
       </c>
@@ -1700,8 +1786,11 @@
       <c r="H8" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>1019930</v>
       </c>
@@ -1726,8 +1815,11 @@
       <c r="H9" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>1022427</v>
       </c>
@@ -1752,8 +1844,11 @@
       <c r="H10" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1023759</v>
       </c>
@@ -1778,8 +1873,11 @@
       <c r="H11" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1024418</v>
       </c>
@@ -1804,8 +1902,11 @@
       <c r="H12" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>1025528</v>
       </c>
@@ -1830,8 +1931,11 @@
       <c r="H13" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>1028175</v>
       </c>
@@ -1856,8 +1960,11 @@
       <c r="H14" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>1028230</v>
       </c>
@@ -1882,8 +1989,11 @@
       <c r="H15" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>1029117</v>
       </c>
@@ -1908,8 +2018,11 @@
       <c r="H16" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1032600</v>
       </c>
@@ -1934,8 +2047,11 @@
       <c r="H17" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>1033605</v>
       </c>
@@ -1960,8 +2076,11 @@
       <c r="H18" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1033971</v>
       </c>
@@ -1986,8 +2105,11 @@
       <c r="H19" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>1034148</v>
       </c>
@@ -2012,8 +2134,11 @@
       <c r="H20" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>1034420</v>
       </c>
@@ -2038,8 +2163,11 @@
       <c r="H21" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>1037110</v>
       </c>
@@ -2064,8 +2192,11 @@
       <c r="H22" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>1038348</v>
       </c>
@@ -2090,8 +2221,11 @@
       <c r="H23" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>1038900</v>
       </c>
@@ -2116,8 +2250,11 @@
       <c r="H24" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>1042486</v>
       </c>
@@ -2142,8 +2279,11 @@
       <c r="H25" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>1044727</v>
       </c>
@@ -2168,8 +2308,11 @@
       <c r="H26" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>1046630</v>
       </c>
@@ -2194,8 +2337,11 @@
       <c r="H27" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>1049135</v>
       </c>
@@ -2220,8 +2366,11 @@
       <c r="H28" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>1051850</v>
       </c>
@@ -2246,8 +2395,11 @@
       <c r="H29" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>1063302</v>
       </c>
@@ -2272,8 +2424,11 @@
       <c r="H30" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>1100507</v>
       </c>
@@ -2298,8 +2453,11 @@
       <c r="H31" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>1103028</v>
       </c>
@@ -2324,8 +2482,11 @@
       <c r="H32" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1106416</v>
       </c>
@@ -2350,8 +2511,11 @@
       <c r="H33" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1109530</v>
       </c>
@@ -2376,8 +2540,11 @@
       <c r="H34" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>1115667</v>
       </c>
@@ -2402,8 +2569,11 @@
       <c r="H35" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1118525</v>
       </c>
@@ -2428,8 +2598,11 @@
       <c r="H36" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1120357</v>
       </c>
@@ -2454,8 +2627,11 @@
       <c r="H37" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1123647</v>
       </c>
@@ -2480,8 +2656,11 @@
       <c r="H38" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1126564</v>
       </c>
@@ -2506,8 +2685,11 @@
       <c r="H39" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1126566</v>
       </c>
@@ -2532,8 +2714,11 @@
       <c r="H40" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>1128965</v>
       </c>
@@ -2558,8 +2743,11 @@
       <c r="H41" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>1129192</v>
       </c>
@@ -2584,8 +2772,11 @@
       <c r="H42" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>1130578</v>
       </c>
@@ -2610,8 +2801,11 @@
       <c r="H43" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1131993</v>
       </c>
@@ -2636,8 +2830,11 @@
       <c r="H44" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>1154674</v>
       </c>
@@ -2662,8 +2859,11 @@
       <c r="H45" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>1161877</v>
       </c>
@@ -2688,8 +2888,11 @@
       <c r="H46" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>1164318</v>
       </c>
@@ -2714,8 +2917,11 @@
       <c r="H47" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>1165451</v>
       </c>
@@ -2740,8 +2946,11 @@
       <c r="H48" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>1166805</v>
       </c>
@@ -2766,8 +2975,11 @@
       <c r="H49" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>1167234</v>
       </c>
@@ -2792,8 +3004,11 @@
       <c r="H50" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>1167773</v>
       </c>
@@ -2818,8 +3033,11 @@
       <c r="H51" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>1168471</v>
       </c>
@@ -2844,8 +3062,11 @@
       <c r="H52" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>1169103</v>
       </c>
@@ -2870,8 +3091,11 @@
       <c r="H53" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I53" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>1169157</v>
       </c>
@@ -2896,8 +3120,11 @@
       <c r="H54" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>1172040</v>
       </c>
@@ -2922,8 +3149,11 @@
       <c r="H55" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>1175378</v>
       </c>
@@ -2948,8 +3178,11 @@
       <c r="H56" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>1176750</v>
       </c>
@@ -2974,8 +3207,11 @@
       <c r="H57" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>1178675</v>
       </c>
@@ -3000,8 +3236,11 @@
       <c r="H58" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>1178823</v>
       </c>
@@ -3026,8 +3265,11 @@
       <c r="H59" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>1179587</v>
       </c>
@@ -3052,8 +3294,11 @@
       <c r="H60" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>1181412</v>
       </c>
@@ -3078,8 +3323,11 @@
       <c r="H61" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I61" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>1184047</v>
       </c>
@@ -3104,8 +3352,11 @@
       <c r="H62" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>1184938</v>
       </c>
@@ -3130,8 +3381,11 @@
       <c r="H63" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I63" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>1185069</v>
       </c>
@@ -3156,8 +3410,11 @@
       <c r="H64" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I64" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>1185458</v>
       </c>
@@ -3182,8 +3439,11 @@
       <c r="H65" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I65" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>1192019</v>
       </c>
@@ -3208,8 +3468,11 @@
       <c r="H66" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I66" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>1192271</v>
       </c>
@@ -3234,8 +3497,11 @@
       <c r="H67" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I67" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>1202645</v>
       </c>
@@ -3260,8 +3526,11 @@
       <c r="H68" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I68" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>1205342</v>
       </c>
@@ -3286,8 +3555,11 @@
       <c r="H69" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I69" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>1206624</v>
       </c>
@@ -3312,8 +3584,11 @@
       <c r="H70" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I70" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>1207596</v>
       </c>
@@ -3338,8 +3613,11 @@
       <c r="H71" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I71" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>1208057</v>
       </c>
@@ -3364,8 +3642,11 @@
       <c r="H72" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I72" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>1208483</v>
       </c>
@@ -3390,8 +3671,11 @@
       <c r="H73" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I73" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>1209174</v>
       </c>
@@ -3416,8 +3700,11 @@
       <c r="H74" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I74" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>1209192</v>
       </c>
@@ -3442,8 +3729,11 @@
       <c r="H75" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I75" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>1209772</v>
       </c>
@@ -3468,8 +3758,11 @@
       <c r="H76" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>1210073</v>
       </c>
@@ -3494,8 +3787,11 @@
       <c r="H77" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I77" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>1212245</v>
       </c>
@@ -3520,8 +3816,11 @@
       <c r="H78" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I78" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>1213275</v>
       </c>
@@ -3546,8 +3845,11 @@
       <c r="H79" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I79" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>1214463</v>
       </c>
@@ -3572,8 +3874,11 @@
       <c r="H80" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>1215075</v>
       </c>
@@ -3598,8 +3903,11 @@
       <c r="H81" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I81" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>1215946</v>
       </c>
@@ -3624,8 +3932,11 @@
       <c r="H82" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I82" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>1217134</v>
       </c>
@@ -3650,8 +3961,11 @@
       <c r="H83" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>1218115</v>
       </c>
@@ -3676,8 +3990,11 @@
       <c r="H84" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I84" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>1221485</v>
       </c>
@@ -3702,8 +4019,11 @@
       <c r="H85" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I85" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>1221878</v>
       </c>
@@ -3728,8 +4048,11 @@
       <c r="H86" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I86" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>1223442</v>
       </c>
@@ -3754,8 +4077,11 @@
       <c r="H87" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I87" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>1223767</v>
       </c>
@@ -3780,8 +4106,11 @@
       <c r="H88" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I88" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>1223826</v>
       </c>
@@ -3806,8 +4135,11 @@
       <c r="H89" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I89" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>1224555</v>
       </c>
@@ -3832,8 +4164,11 @@
       <c r="H90" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I90" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>1224629</v>
       </c>
@@ -3858,8 +4193,11 @@
       <c r="H91" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I91" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>1224679</v>
       </c>
@@ -3884,8 +4222,11 @@
       <c r="H92" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I92" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>1224833</v>
       </c>
@@ -3910,8 +4251,11 @@
       <c r="H93" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I93" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>1225440</v>
       </c>
@@ -3936,8 +4280,11 @@
       <c r="H94" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I94" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>1225505</v>
       </c>
@@ -3962,8 +4309,11 @@
       <c r="H95" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I95" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>1225966</v>
       </c>
@@ -3988,8 +4338,11 @@
       <c r="H96" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I96" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>1226038</v>
       </c>
@@ -4014,8 +4367,11 @@
       <c r="H97" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I97" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>1227748</v>
       </c>
@@ -4040,8 +4396,11 @@
       <c r="H98" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I98" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>1227960</v>
       </c>
@@ -4066,8 +4425,11 @@
       <c r="H99" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I99" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>1228414</v>
       </c>
@@ -4092,8 +4454,11 @@
       <c r="H100" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I100" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>1228651</v>
       </c>
@@ -4118,8 +4483,11 @@
       <c r="H101" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I101" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>1230176</v>
       </c>
@@ -4144,8 +4512,11 @@
       <c r="H102" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I102" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>1230888</v>
       </c>
@@ -4170,8 +4541,11 @@
       <c r="H103" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I103" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>1230945</v>
       </c>
@@ -4196,8 +4570,11 @@
       <c r="H104" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I104" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>3000014</v>
       </c>
@@ -4222,8 +4599,11 @@
       <c r="H105" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I105" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>3000014</v>
       </c>
@@ -4248,8 +4628,11 @@
       <c r="H106" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I106" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>3000014</v>
       </c>
@@ -4274,8 +4657,11 @@
       <c r="H107" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I107" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>3000071</v>
       </c>
@@ -4300,8 +4686,11 @@
       <c r="H108" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I108" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>3000155</v>
       </c>
@@ -4326,8 +4715,11 @@
       <c r="H109" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I109" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>3000748</v>
       </c>
@@ -4352,8 +4744,11 @@
       <c r="H110" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I110" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>3000851</v>
       </c>
@@ -4378,8 +4773,11 @@
       <c r="H111" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I111" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>3000889</v>
       </c>
@@ -4404,8 +4802,11 @@
       <c r="H112" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I112" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>3001329</v>
       </c>
@@ -4430,8 +4831,11 @@
       <c r="H113" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I113" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>3001467</v>
       </c>
@@ -4456,8 +4860,11 @@
       <c r="H114" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I114" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>3001624</v>
       </c>
@@ -4482,8 +4889,11 @@
       <c r="H115" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I115" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>3001673</v>
       </c>
@@ -4508,8 +4918,11 @@
       <c r="H116" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I116" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>3001710</v>
       </c>
@@ -4534,8 +4947,11 @@
       <c r="H117" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I117" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>3001712</v>
       </c>
@@ -4560,8 +4976,11 @@
       <c r="H118" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I118" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>3001850</v>
       </c>
@@ -4586,8 +5005,11 @@
       <c r="H119" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I119" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>3001905</v>
       </c>
@@ -4612,8 +5034,11 @@
       <c r="H120" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I120" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>3001928</v>
       </c>
@@ -4638,8 +5063,11 @@
       <c r="H121" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I121" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>3001973</v>
       </c>
@@ -4664,8 +5092,11 @@
       <c r="H122" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I122" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>3001975</v>
       </c>
@@ -4690,8 +5121,11 @@
       <c r="H123" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I123" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>3002192</v>
       </c>
@@ -4716,8 +5150,11 @@
       <c r="H124" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I124" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>3002225</v>
       </c>
@@ -4742,8 +5179,11 @@
       <c r="H125" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I125" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>3002382</v>
       </c>
@@ -4768,8 +5208,11 @@
       <c r="H126" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I126" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>3003758</v>
       </c>
@@ -4794,8 +5237,11 @@
       <c r="H127" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I127" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>3003802</v>
       </c>
@@ -4820,8 +5266,11 @@
       <c r="H128" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I128" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>3005657</v>
       </c>
@@ -4846,8 +5295,11 @@
       <c r="H129" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I129" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>3005658</v>
       </c>
@@ -4872,8 +5324,11 @@
       <c r="H130" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I130" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>3006064</v>
       </c>
@@ -4898,8 +5353,11 @@
       <c r="H131" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I131" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>3006396</v>
       </c>
@@ -4924,8 +5382,11 @@
       <c r="H132" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I132" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>3006601</v>
       </c>
@@ -4950,8 +5411,11 @@
       <c r="H133" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I133" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>3006875</v>
       </c>
@@ -4976,8 +5440,11 @@
       <c r="H134" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I134" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>3007162</v>
       </c>
@@ -5002,8 +5469,11 @@
       <c r="H135" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I135" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>3007459</v>
       </c>
@@ -5028,8 +5498,11 @@
       <c r="H136" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I136" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>3008125</v>
       </c>
@@ -5054,8 +5527,11 @@
       <c r="H137" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I137" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>3008285</v>
       </c>
@@ -5080,8 +5556,11 @@
       <c r="H138" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I138" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>3008380</v>
       </c>
@@ -5106,8 +5585,11 @@
       <c r="H139" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I139" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>3010877</v>
       </c>
@@ -5132,8 +5614,11 @@
       <c r="H140" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I140" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>3011296</v>
       </c>
@@ -5158,8 +5643,11 @@
       <c r="H141" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I141" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>3011921</v>
       </c>
@@ -5184,8 +5672,11 @@
       <c r="H142" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I142" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>3014142</v>
       </c>
@@ -5210,8 +5701,11 @@
       <c r="H143" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I143" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>3014195</v>
       </c>
@@ -5236,8 +5730,11 @@
       <c r="H144" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I144" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>3014947</v>
       </c>
@@ -5262,8 +5759,11 @@
       <c r="H145" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I145" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>3014978</v>
       </c>
@@ -5288,8 +5788,11 @@
       <c r="H146" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I146" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>3015252</v>
       </c>
@@ -5314,8 +5817,11 @@
       <c r="H147" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I147" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>3020958</v>
       </c>
@@ -5340,8 +5846,11 @@
       <c r="H148" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I148" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>3021204</v>
       </c>
@@ -5366,8 +5875,11 @@
       <c r="H149" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I149" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>3021970</v>
       </c>
@@ -5392,8 +5904,11 @@
       <c r="H150" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I150" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>3022191</v>
       </c>
@@ -5418,8 +5933,11 @@
       <c r="H151" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I151" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>3022206</v>
       </c>
@@ -5444,8 +5962,11 @@
       <c r="H152" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I152" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>3022389</v>
       </c>
@@ -5470,8 +5991,11 @@
       <c r="H153" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I153" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>3023114</v>
       </c>
@@ -5496,8 +6020,11 @@
       <c r="H154" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I154" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>3023115</v>
       </c>
@@ -5522,8 +6049,11 @@
       <c r="H155" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I155" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>3023414</v>
       </c>
@@ -5548,8 +6078,11 @@
       <c r="H156" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I156" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>3023812</v>
       </c>
@@ -5574,8 +6107,11 @@
       <c r="H157" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I157" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>3023813</v>
       </c>
@@ -5600,8 +6136,11 @@
       <c r="H158" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I158" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
         <v>3023814</v>
       </c>
@@ -5626,8 +6165,11 @@
       <c r="H159" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I159" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <v>3023815</v>
       </c>
@@ -5652,8 +6194,11 @@
       <c r="H160" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I160" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>3023818</v>
       </c>
@@ -5678,8 +6223,11 @@
       <c r="H161" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I161" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>3023841</v>
       </c>
@@ -5704,8 +6252,11 @@
       <c r="H162" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I162" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <v>3023847</v>
       </c>
@@ -5730,8 +6281,11 @@
       <c r="H163" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I163" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>3023857</v>
       </c>
@@ -5756,8 +6310,11 @@
       <c r="H164" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I164" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <v>3023858</v>
       </c>
@@ -5782,8 +6339,11 @@
       <c r="H165" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I165" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <v>3023861</v>
       </c>
@@ -5808,8 +6368,11 @@
       <c r="H166" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I166" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>3023870</v>
       </c>
@@ -5834,8 +6397,11 @@
       <c r="H167" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I167" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <v>3023921</v>
       </c>
@@ -5860,8 +6426,11 @@
       <c r="H168" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I168" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>3025188</v>
       </c>
@@ -5886,8 +6455,11 @@
       <c r="H169" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I169" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
         <v>3025234</v>
       </c>
@@ -5912,8 +6484,11 @@
       <c r="H170" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I170" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>3025276</v>
       </c>
@@ -5938,8 +6513,11 @@
       <c r="H171" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I171" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>3026113</v>
       </c>
@@ -5964,8 +6542,11 @@
       <c r="H172" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I172" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>3027576</v>
       </c>
@@ -5990,8 +6571,11 @@
       <c r="H173" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I173" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>3028794</v>
       </c>
@@ -6015,10 +6599,2970 @@
       </c>
       <c r="H174" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="I174" s="8" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H174" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5965FC7F-2C9A-4491-936B-05468969C809}">
+  <dimension ref="A1:E173"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1001535</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1001535</v>
+      </c>
+      <c r="C2" s="6">
+        <v>6</v>
+      </c>
+      <c r="D2" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>1005000</v>
+      </c>
+      <c r="B3" s="6">
+        <v>1005000</v>
+      </c>
+      <c r="C3" s="6">
+        <v>6</v>
+      </c>
+      <c r="D3" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3025788</v>
+      </c>
+      <c r="B4" s="6">
+        <v>1006513</v>
+      </c>
+      <c r="C4" s="6">
+        <v>6</v>
+      </c>
+      <c r="D4" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>1011370</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1011370</v>
+      </c>
+      <c r="C5" s="6">
+        <v>6</v>
+      </c>
+      <c r="D5" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>1013940</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1013940</v>
+      </c>
+      <c r="C6" s="6">
+        <v>6</v>
+      </c>
+      <c r="D6" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>1014465</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1014465</v>
+      </c>
+      <c r="C7" s="6">
+        <v>6</v>
+      </c>
+      <c r="D7" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>1018585</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1018585</v>
+      </c>
+      <c r="C8" s="6">
+        <v>6</v>
+      </c>
+      <c r="D8" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>1019930</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1019930</v>
+      </c>
+      <c r="C9" s="6">
+        <v>6</v>
+      </c>
+      <c r="D9" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>1022427</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1022427</v>
+      </c>
+      <c r="C10" s="6">
+        <v>6</v>
+      </c>
+      <c r="D10" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>1023759</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1023759</v>
+      </c>
+      <c r="C11" s="6">
+        <v>6</v>
+      </c>
+      <c r="D11" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>1024418</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1024418</v>
+      </c>
+      <c r="C12" s="6">
+        <v>6</v>
+      </c>
+      <c r="D12" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>1025528</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1025528</v>
+      </c>
+      <c r="C13" s="6">
+        <v>6</v>
+      </c>
+      <c r="D13" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>1028175</v>
+      </c>
+      <c r="B14" s="6">
+        <v>1028175</v>
+      </c>
+      <c r="C14" s="6">
+        <v>6</v>
+      </c>
+      <c r="D14" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>1028230</v>
+      </c>
+      <c r="B15" s="6">
+        <v>1028230</v>
+      </c>
+      <c r="C15" s="6">
+        <v>6</v>
+      </c>
+      <c r="D15" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>1029117</v>
+      </c>
+      <c r="B16" s="6">
+        <v>1029117</v>
+      </c>
+      <c r="C16" s="6">
+        <v>6</v>
+      </c>
+      <c r="D16" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>1032600</v>
+      </c>
+      <c r="B17" s="6">
+        <v>1032600</v>
+      </c>
+      <c r="C17" s="6">
+        <v>6</v>
+      </c>
+      <c r="D17" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>1033605</v>
+      </c>
+      <c r="B18" s="6">
+        <v>1033605</v>
+      </c>
+      <c r="C18" s="6">
+        <v>6</v>
+      </c>
+      <c r="D18" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>1033971</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1033971</v>
+      </c>
+      <c r="C19" s="6">
+        <v>6</v>
+      </c>
+      <c r="D19" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>1034148</v>
+      </c>
+      <c r="B20" s="6">
+        <v>1034148</v>
+      </c>
+      <c r="C20" s="6">
+        <v>6</v>
+      </c>
+      <c r="D20" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>1034420</v>
+      </c>
+      <c r="B21" s="6">
+        <v>1034420</v>
+      </c>
+      <c r="C21" s="6">
+        <v>6</v>
+      </c>
+      <c r="D21" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>1037110</v>
+      </c>
+      <c r="B22" s="6">
+        <v>1037110</v>
+      </c>
+      <c r="C22" s="6">
+        <v>6</v>
+      </c>
+      <c r="D22" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>1038348</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1038348</v>
+      </c>
+      <c r="C23" s="6">
+        <v>6</v>
+      </c>
+      <c r="D23" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>1038900</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1038900</v>
+      </c>
+      <c r="C24" s="6">
+        <v>6</v>
+      </c>
+      <c r="D24" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>1042486</v>
+      </c>
+      <c r="B25" s="6">
+        <v>1042486</v>
+      </c>
+      <c r="C25" s="6">
+        <v>6</v>
+      </c>
+      <c r="D25" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>1044727</v>
+      </c>
+      <c r="B26" s="6">
+        <v>1044727</v>
+      </c>
+      <c r="C26" s="6">
+        <v>6</v>
+      </c>
+      <c r="D26" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>1046630</v>
+      </c>
+      <c r="B27" s="6">
+        <v>1046630</v>
+      </c>
+      <c r="C27" s="6">
+        <v>6</v>
+      </c>
+      <c r="D27" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>1049135</v>
+      </c>
+      <c r="B28" s="6">
+        <v>1049135</v>
+      </c>
+      <c r="C28" s="6">
+        <v>6</v>
+      </c>
+      <c r="D28" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>1051850</v>
+      </c>
+      <c r="B29" s="6">
+        <v>1051850</v>
+      </c>
+      <c r="C29" s="6">
+        <v>6</v>
+      </c>
+      <c r="D29" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>1063302</v>
+      </c>
+      <c r="B30" s="6">
+        <v>1063302</v>
+      </c>
+      <c r="C30" s="6">
+        <v>6</v>
+      </c>
+      <c r="D30" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>1100507</v>
+      </c>
+      <c r="B31" s="6">
+        <v>1100507</v>
+      </c>
+      <c r="C31" s="6">
+        <v>6</v>
+      </c>
+      <c r="D31" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>1103028</v>
+      </c>
+      <c r="B32" s="6">
+        <v>1103028</v>
+      </c>
+      <c r="C32" s="6">
+        <v>6</v>
+      </c>
+      <c r="D32" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>1106416</v>
+      </c>
+      <c r="B33" s="6">
+        <v>1106416</v>
+      </c>
+      <c r="C33" s="6">
+        <v>6</v>
+      </c>
+      <c r="D33" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>1109530</v>
+      </c>
+      <c r="B34" s="6">
+        <v>1109530</v>
+      </c>
+      <c r="C34" s="6">
+        <v>6</v>
+      </c>
+      <c r="D34" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>1115667</v>
+      </c>
+      <c r="B35" s="6">
+        <v>1115667</v>
+      </c>
+      <c r="C35" s="6">
+        <v>6</v>
+      </c>
+      <c r="D35" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>1118525</v>
+      </c>
+      <c r="B36" s="6">
+        <v>1118525</v>
+      </c>
+      <c r="C36" s="6">
+        <v>6</v>
+      </c>
+      <c r="D36" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>1120357</v>
+      </c>
+      <c r="B37" s="6">
+        <v>1120357</v>
+      </c>
+      <c r="C37" s="6">
+        <v>6</v>
+      </c>
+      <c r="D37" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>1123647</v>
+      </c>
+      <c r="B38" s="6">
+        <v>1123647</v>
+      </c>
+      <c r="C38" s="6">
+        <v>6</v>
+      </c>
+      <c r="D38" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>1126564</v>
+      </c>
+      <c r="B39" s="6">
+        <v>1126564</v>
+      </c>
+      <c r="C39" s="6">
+        <v>6</v>
+      </c>
+      <c r="D39" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>1128965</v>
+      </c>
+      <c r="B40" s="6">
+        <v>1128965</v>
+      </c>
+      <c r="C40" s="6">
+        <v>6</v>
+      </c>
+      <c r="D40" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>1129192</v>
+      </c>
+      <c r="B41" s="6">
+        <v>1129192</v>
+      </c>
+      <c r="C41" s="6">
+        <v>6</v>
+      </c>
+      <c r="D41" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>1130578</v>
+      </c>
+      <c r="B42" s="6">
+        <v>1130578</v>
+      </c>
+      <c r="C42" s="6">
+        <v>6</v>
+      </c>
+      <c r="D42" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>1131993</v>
+      </c>
+      <c r="B43" s="6">
+        <v>1131993</v>
+      </c>
+      <c r="C43" s="6">
+        <v>6</v>
+      </c>
+      <c r="D43" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>1154674</v>
+      </c>
+      <c r="B44" s="6">
+        <v>1154674</v>
+      </c>
+      <c r="C44" s="6">
+        <v>6</v>
+      </c>
+      <c r="D44" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>1161877</v>
+      </c>
+      <c r="B45" s="6">
+        <v>1161877</v>
+      </c>
+      <c r="C45" s="6">
+        <v>6</v>
+      </c>
+      <c r="D45" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>1164318</v>
+      </c>
+      <c r="B46" s="6">
+        <v>1164318</v>
+      </c>
+      <c r="C46" s="6">
+        <v>6</v>
+      </c>
+      <c r="D46" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>1165451</v>
+      </c>
+      <c r="B47" s="6">
+        <v>1165451</v>
+      </c>
+      <c r="C47" s="6">
+        <v>6</v>
+      </c>
+      <c r="D47" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>1166805</v>
+      </c>
+      <c r="B48" s="6">
+        <v>1166805</v>
+      </c>
+      <c r="C48" s="6">
+        <v>6</v>
+      </c>
+      <c r="D48" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>1167234</v>
+      </c>
+      <c r="B49" s="6">
+        <v>1167234</v>
+      </c>
+      <c r="C49" s="6">
+        <v>6</v>
+      </c>
+      <c r="D49" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>1167773</v>
+      </c>
+      <c r="B50" s="6">
+        <v>1167773</v>
+      </c>
+      <c r="C50" s="6">
+        <v>6</v>
+      </c>
+      <c r="D50" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>1168471</v>
+      </c>
+      <c r="B51" s="6">
+        <v>1168471</v>
+      </c>
+      <c r="C51" s="6">
+        <v>6</v>
+      </c>
+      <c r="D51" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>1169103</v>
+      </c>
+      <c r="B52" s="6">
+        <v>1169103</v>
+      </c>
+      <c r="C52" s="6">
+        <v>6</v>
+      </c>
+      <c r="D52" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>1169157</v>
+      </c>
+      <c r="B53" s="6">
+        <v>1169157</v>
+      </c>
+      <c r="C53" s="6">
+        <v>6</v>
+      </c>
+      <c r="D53" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>1172040</v>
+      </c>
+      <c r="B54" s="6">
+        <v>1172040</v>
+      </c>
+      <c r="C54" s="6">
+        <v>6</v>
+      </c>
+      <c r="D54" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>1175378</v>
+      </c>
+      <c r="B55" s="6">
+        <v>1175378</v>
+      </c>
+      <c r="C55" s="6">
+        <v>6</v>
+      </c>
+      <c r="D55" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>1176750</v>
+      </c>
+      <c r="B56" s="6">
+        <v>1176750</v>
+      </c>
+      <c r="C56" s="6">
+        <v>6</v>
+      </c>
+      <c r="D56" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>1178675</v>
+      </c>
+      <c r="B57" s="6">
+        <v>1178675</v>
+      </c>
+      <c r="C57" s="6">
+        <v>6</v>
+      </c>
+      <c r="D57" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>1178823</v>
+      </c>
+      <c r="B58" s="6">
+        <v>1178823</v>
+      </c>
+      <c r="C58" s="6">
+        <v>6</v>
+      </c>
+      <c r="D58" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>1179587</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1179587</v>
+      </c>
+      <c r="C59" s="6">
+        <v>6</v>
+      </c>
+      <c r="D59" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>1181412</v>
+      </c>
+      <c r="B60" s="6">
+        <v>1181412</v>
+      </c>
+      <c r="C60" s="6">
+        <v>6</v>
+      </c>
+      <c r="D60" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>1184047</v>
+      </c>
+      <c r="B61" s="6">
+        <v>1184047</v>
+      </c>
+      <c r="C61" s="6">
+        <v>6</v>
+      </c>
+      <c r="D61" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>1184938</v>
+      </c>
+      <c r="B62" s="6">
+        <v>1184938</v>
+      </c>
+      <c r="C62" s="6">
+        <v>6</v>
+      </c>
+      <c r="D62" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>1185069</v>
+      </c>
+      <c r="B63" s="6">
+        <v>1185069</v>
+      </c>
+      <c r="C63" s="6">
+        <v>6</v>
+      </c>
+      <c r="D63" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>1185458</v>
+      </c>
+      <c r="B64" s="6">
+        <v>1185458</v>
+      </c>
+      <c r="C64" s="6">
+        <v>6</v>
+      </c>
+      <c r="D64" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>1192019</v>
+      </c>
+      <c r="B65" s="6">
+        <v>1192019</v>
+      </c>
+      <c r="C65" s="6">
+        <v>6</v>
+      </c>
+      <c r="D65" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>1192271</v>
+      </c>
+      <c r="B66" s="6">
+        <v>1192271</v>
+      </c>
+      <c r="C66" s="6">
+        <v>6</v>
+      </c>
+      <c r="D66" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>1202645</v>
+      </c>
+      <c r="B67" s="6">
+        <v>1202645</v>
+      </c>
+      <c r="C67" s="6">
+        <v>6</v>
+      </c>
+      <c r="D67" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>1205342</v>
+      </c>
+      <c r="B68" s="6">
+        <v>1205342</v>
+      </c>
+      <c r="C68" s="6">
+        <v>6</v>
+      </c>
+      <c r="D68" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>1206624</v>
+      </c>
+      <c r="B69" s="6">
+        <v>1206624</v>
+      </c>
+      <c r="C69" s="6">
+        <v>6</v>
+      </c>
+      <c r="D69" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>1207596</v>
+      </c>
+      <c r="B70" s="6">
+        <v>1207596</v>
+      </c>
+      <c r="C70" s="6">
+        <v>6</v>
+      </c>
+      <c r="D70" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>1208057</v>
+      </c>
+      <c r="B71" s="6">
+        <v>1208057</v>
+      </c>
+      <c r="C71" s="6">
+        <v>6</v>
+      </c>
+      <c r="D71" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>1208483</v>
+      </c>
+      <c r="B72" s="6">
+        <v>1208483</v>
+      </c>
+      <c r="C72" s="6">
+        <v>6</v>
+      </c>
+      <c r="D72" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>1209174</v>
+      </c>
+      <c r="B73" s="6">
+        <v>1209174</v>
+      </c>
+      <c r="C73" s="6">
+        <v>6</v>
+      </c>
+      <c r="D73" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>1209192</v>
+      </c>
+      <c r="B74" s="6">
+        <v>1209192</v>
+      </c>
+      <c r="C74" s="6">
+        <v>6</v>
+      </c>
+      <c r="D74" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>1209772</v>
+      </c>
+      <c r="B75" s="6">
+        <v>1209772</v>
+      </c>
+      <c r="C75" s="6">
+        <v>6</v>
+      </c>
+      <c r="D75" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>1210073</v>
+      </c>
+      <c r="B76" s="6">
+        <v>1210073</v>
+      </c>
+      <c r="C76" s="6">
+        <v>6</v>
+      </c>
+      <c r="D76" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>1212245</v>
+      </c>
+      <c r="B77" s="6">
+        <v>1212245</v>
+      </c>
+      <c r="C77" s="6">
+        <v>6</v>
+      </c>
+      <c r="D77" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>1213275</v>
+      </c>
+      <c r="B78" s="6">
+        <v>1213275</v>
+      </c>
+      <c r="C78" s="6">
+        <v>6</v>
+      </c>
+      <c r="D78" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>1214463</v>
+      </c>
+      <c r="B79" s="6">
+        <v>1214463</v>
+      </c>
+      <c r="C79" s="6">
+        <v>6</v>
+      </c>
+      <c r="D79" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>1215075</v>
+      </c>
+      <c r="B80" s="6">
+        <v>1215075</v>
+      </c>
+      <c r="C80" s="6">
+        <v>6</v>
+      </c>
+      <c r="D80" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>1215946</v>
+      </c>
+      <c r="B81" s="6">
+        <v>1215946</v>
+      </c>
+      <c r="C81" s="6">
+        <v>6</v>
+      </c>
+      <c r="D81" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>1217134</v>
+      </c>
+      <c r="B82" s="6">
+        <v>1217134</v>
+      </c>
+      <c r="C82" s="6">
+        <v>6</v>
+      </c>
+      <c r="D82" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>1218115</v>
+      </c>
+      <c r="B83" s="6">
+        <v>1218115</v>
+      </c>
+      <c r="C83" s="6">
+        <v>6</v>
+      </c>
+      <c r="D83" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>1221485</v>
+      </c>
+      <c r="B84" s="6">
+        <v>1221485</v>
+      </c>
+      <c r="C84" s="6">
+        <v>6</v>
+      </c>
+      <c r="D84" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>1221878</v>
+      </c>
+      <c r="B85" s="6">
+        <v>1221878</v>
+      </c>
+      <c r="C85" s="6">
+        <v>6</v>
+      </c>
+      <c r="D85" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>1223442</v>
+      </c>
+      <c r="B86" s="6">
+        <v>1223442</v>
+      </c>
+      <c r="C86" s="6">
+        <v>6</v>
+      </c>
+      <c r="D86" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>1223767</v>
+      </c>
+      <c r="B87" s="6">
+        <v>1223767</v>
+      </c>
+      <c r="C87" s="6">
+        <v>6</v>
+      </c>
+      <c r="D87" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>1223826</v>
+      </c>
+      <c r="B88" s="6">
+        <v>1223826</v>
+      </c>
+      <c r="C88" s="6">
+        <v>6</v>
+      </c>
+      <c r="D88" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>1224555</v>
+      </c>
+      <c r="B89" s="6">
+        <v>1224555</v>
+      </c>
+      <c r="C89" s="6">
+        <v>6</v>
+      </c>
+      <c r="D89" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>1224629</v>
+      </c>
+      <c r="B90" s="6">
+        <v>1224629</v>
+      </c>
+      <c r="C90" s="6">
+        <v>6</v>
+      </c>
+      <c r="D90" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>1224679</v>
+      </c>
+      <c r="B91" s="6">
+        <v>1224679</v>
+      </c>
+      <c r="C91" s="6">
+        <v>6</v>
+      </c>
+      <c r="D91" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>1224833</v>
+      </c>
+      <c r="B92" s="6">
+        <v>1224833</v>
+      </c>
+      <c r="C92" s="6">
+        <v>6</v>
+      </c>
+      <c r="D92" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>1225440</v>
+      </c>
+      <c r="B93" s="6">
+        <v>1225440</v>
+      </c>
+      <c r="C93" s="6">
+        <v>6</v>
+      </c>
+      <c r="D93" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>1225505</v>
+      </c>
+      <c r="B94" s="6">
+        <v>1225505</v>
+      </c>
+      <c r="C94" s="6">
+        <v>6</v>
+      </c>
+      <c r="D94" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>1225966</v>
+      </c>
+      <c r="B95" s="6">
+        <v>1225966</v>
+      </c>
+      <c r="C95" s="6">
+        <v>6</v>
+      </c>
+      <c r="D95" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>1226038</v>
+      </c>
+      <c r="B96" s="6">
+        <v>1226038</v>
+      </c>
+      <c r="C96" s="6">
+        <v>6</v>
+      </c>
+      <c r="D96" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>1227748</v>
+      </c>
+      <c r="B97" s="6">
+        <v>1227748</v>
+      </c>
+      <c r="C97" s="6">
+        <v>6</v>
+      </c>
+      <c r="D97" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>1227960</v>
+      </c>
+      <c r="B98" s="6">
+        <v>1227960</v>
+      </c>
+      <c r="C98" s="6">
+        <v>6</v>
+      </c>
+      <c r="D98" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>1228414</v>
+      </c>
+      <c r="B99" s="6">
+        <v>1228414</v>
+      </c>
+      <c r="C99" s="6">
+        <v>6</v>
+      </c>
+      <c r="D99" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>1228651</v>
+      </c>
+      <c r="B100" s="6">
+        <v>1228651</v>
+      </c>
+      <c r="C100" s="6">
+        <v>6</v>
+      </c>
+      <c r="D100" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>1230176</v>
+      </c>
+      <c r="B101" s="6">
+        <v>1230176</v>
+      </c>
+      <c r="C101" s="6">
+        <v>6</v>
+      </c>
+      <c r="D101" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>1230888</v>
+      </c>
+      <c r="B102" s="6">
+        <v>1230888</v>
+      </c>
+      <c r="C102" s="6">
+        <v>6</v>
+      </c>
+      <c r="D102" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>1230945</v>
+      </c>
+      <c r="B103" s="6">
+        <v>1230945</v>
+      </c>
+      <c r="C103" s="6">
+        <v>6</v>
+      </c>
+      <c r="D103" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>1120829</v>
+      </c>
+      <c r="B104" s="6">
+        <v>3000014</v>
+      </c>
+      <c r="C104" s="6">
+        <v>6</v>
+      </c>
+      <c r="D104" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>1122428</v>
+      </c>
+      <c r="B105" s="6">
+        <v>3000014</v>
+      </c>
+      <c r="C105" s="6">
+        <v>6</v>
+      </c>
+      <c r="D105" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>1130038</v>
+      </c>
+      <c r="B106" s="6">
+        <v>3000014</v>
+      </c>
+      <c r="C106" s="6">
+        <v>6</v>
+      </c>
+      <c r="D106" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>3000071</v>
+      </c>
+      <c r="B107" s="6">
+        <v>3000071</v>
+      </c>
+      <c r="C107" s="6">
+        <v>6</v>
+      </c>
+      <c r="D107" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>3000155</v>
+      </c>
+      <c r="B108" s="6">
+        <v>3000155</v>
+      </c>
+      <c r="C108" s="6">
+        <v>6</v>
+      </c>
+      <c r="D108" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>3000748</v>
+      </c>
+      <c r="B109" s="6">
+        <v>3000748</v>
+      </c>
+      <c r="C109" s="6">
+        <v>6</v>
+      </c>
+      <c r="D109" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>3000851</v>
+      </c>
+      <c r="B110" s="6">
+        <v>3000851</v>
+      </c>
+      <c r="C110" s="6">
+        <v>6</v>
+      </c>
+      <c r="D110" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>3000889</v>
+      </c>
+      <c r="B111" s="6">
+        <v>3000889</v>
+      </c>
+      <c r="C111" s="6">
+        <v>6</v>
+      </c>
+      <c r="D111" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>3001329</v>
+      </c>
+      <c r="B112" s="6">
+        <v>3001329</v>
+      </c>
+      <c r="C112" s="6">
+        <v>6</v>
+      </c>
+      <c r="D112" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>3001467</v>
+      </c>
+      <c r="B113" s="6">
+        <v>3001467</v>
+      </c>
+      <c r="C113" s="6">
+        <v>6</v>
+      </c>
+      <c r="D113" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>3001624</v>
+      </c>
+      <c r="B114" s="6">
+        <v>3001624</v>
+      </c>
+      <c r="C114" s="6">
+        <v>6</v>
+      </c>
+      <c r="D114" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>3001673</v>
+      </c>
+      <c r="B115" s="6">
+        <v>3001673</v>
+      </c>
+      <c r="C115" s="6">
+        <v>6</v>
+      </c>
+      <c r="D115" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>3001710</v>
+      </c>
+      <c r="B116" s="6">
+        <v>3001710</v>
+      </c>
+      <c r="C116" s="6">
+        <v>6</v>
+      </c>
+      <c r="D116" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>3001712</v>
+      </c>
+      <c r="B117" s="6">
+        <v>3001712</v>
+      </c>
+      <c r="C117" s="6">
+        <v>6</v>
+      </c>
+      <c r="D117" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>3001850</v>
+      </c>
+      <c r="B118" s="6">
+        <v>3001850</v>
+      </c>
+      <c r="C118" s="6">
+        <v>6</v>
+      </c>
+      <c r="D118" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>3001905</v>
+      </c>
+      <c r="B119" s="6">
+        <v>3001905</v>
+      </c>
+      <c r="C119" s="6">
+        <v>6</v>
+      </c>
+      <c r="D119" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>3001928</v>
+      </c>
+      <c r="B120" s="6">
+        <v>3001928</v>
+      </c>
+      <c r="C120" s="6">
+        <v>6</v>
+      </c>
+      <c r="D120" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>3001973</v>
+      </c>
+      <c r="B121" s="6">
+        <v>3001973</v>
+      </c>
+      <c r="C121" s="6">
+        <v>6</v>
+      </c>
+      <c r="D121" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>3001975</v>
+      </c>
+      <c r="B122" s="6">
+        <v>3001975</v>
+      </c>
+      <c r="C122" s="6">
+        <v>6</v>
+      </c>
+      <c r="D122" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>3002192</v>
+      </c>
+      <c r="B123" s="6">
+        <v>3002192</v>
+      </c>
+      <c r="C123" s="6">
+        <v>6</v>
+      </c>
+      <c r="D123" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>3002225</v>
+      </c>
+      <c r="B124" s="6">
+        <v>3002225</v>
+      </c>
+      <c r="C124" s="6">
+        <v>6</v>
+      </c>
+      <c r="D124" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>3002382</v>
+      </c>
+      <c r="B125" s="6">
+        <v>3002382</v>
+      </c>
+      <c r="C125" s="6">
+        <v>6</v>
+      </c>
+      <c r="D125" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>3003758</v>
+      </c>
+      <c r="B126" s="6">
+        <v>3003758</v>
+      </c>
+      <c r="C126" s="6">
+        <v>6</v>
+      </c>
+      <c r="D126" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>3003802</v>
+      </c>
+      <c r="B127" s="6">
+        <v>3003802</v>
+      </c>
+      <c r="C127" s="6">
+        <v>6</v>
+      </c>
+      <c r="D127" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>3005657</v>
+      </c>
+      <c r="B128" s="6">
+        <v>3005657</v>
+      </c>
+      <c r="C128" s="6">
+        <v>6</v>
+      </c>
+      <c r="D128" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>3005658</v>
+      </c>
+      <c r="B129" s="6">
+        <v>3005658</v>
+      </c>
+      <c r="C129" s="6">
+        <v>6</v>
+      </c>
+      <c r="D129" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>3006064</v>
+      </c>
+      <c r="B130" s="6">
+        <v>3006064</v>
+      </c>
+      <c r="C130" s="6">
+        <v>6</v>
+      </c>
+      <c r="D130" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>3006396</v>
+      </c>
+      <c r="B131" s="6">
+        <v>3006396</v>
+      </c>
+      <c r="C131" s="6">
+        <v>6</v>
+      </c>
+      <c r="D131" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>3006601</v>
+      </c>
+      <c r="B132" s="6">
+        <v>3006601</v>
+      </c>
+      <c r="C132" s="6">
+        <v>6</v>
+      </c>
+      <c r="D132" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>3006875</v>
+      </c>
+      <c r="B133" s="6">
+        <v>3006875</v>
+      </c>
+      <c r="C133" s="6">
+        <v>6</v>
+      </c>
+      <c r="D133" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>3007162</v>
+      </c>
+      <c r="B134" s="6">
+        <v>3007162</v>
+      </c>
+      <c r="C134" s="6">
+        <v>6</v>
+      </c>
+      <c r="D134" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>3007459</v>
+      </c>
+      <c r="B135" s="6">
+        <v>3007459</v>
+      </c>
+      <c r="C135" s="6">
+        <v>6</v>
+      </c>
+      <c r="D135" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>3008125</v>
+      </c>
+      <c r="B136" s="6">
+        <v>3008125</v>
+      </c>
+      <c r="C136" s="6">
+        <v>6</v>
+      </c>
+      <c r="D136" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>3008285</v>
+      </c>
+      <c r="B137" s="6">
+        <v>3008285</v>
+      </c>
+      <c r="C137" s="6">
+        <v>6</v>
+      </c>
+      <c r="D137" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>3008380</v>
+      </c>
+      <c r="B138" s="6">
+        <v>3008380</v>
+      </c>
+      <c r="C138" s="6">
+        <v>6</v>
+      </c>
+      <c r="D138" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>3010877</v>
+      </c>
+      <c r="B139" s="6">
+        <v>3010877</v>
+      </c>
+      <c r="C139" s="6">
+        <v>6</v>
+      </c>
+      <c r="D139" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>3011296</v>
+      </c>
+      <c r="B140" s="6">
+        <v>3011296</v>
+      </c>
+      <c r="C140" s="6">
+        <v>6</v>
+      </c>
+      <c r="D140" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>3011921</v>
+      </c>
+      <c r="B141" s="6">
+        <v>3011921</v>
+      </c>
+      <c r="C141" s="6">
+        <v>6</v>
+      </c>
+      <c r="D141" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>3014142</v>
+      </c>
+      <c r="B142" s="6">
+        <v>3014142</v>
+      </c>
+      <c r="C142" s="6">
+        <v>6</v>
+      </c>
+      <c r="D142" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>3014195</v>
+      </c>
+      <c r="B143" s="6">
+        <v>3014195</v>
+      </c>
+      <c r="C143" s="6">
+        <v>6</v>
+      </c>
+      <c r="D143" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>3014947</v>
+      </c>
+      <c r="B144" s="6">
+        <v>3014947</v>
+      </c>
+      <c r="C144" s="6">
+        <v>6</v>
+      </c>
+      <c r="D144" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>3014978</v>
+      </c>
+      <c r="B145" s="6">
+        <v>3014978</v>
+      </c>
+      <c r="C145" s="6">
+        <v>6</v>
+      </c>
+      <c r="D145" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>3015252</v>
+      </c>
+      <c r="B146" s="6">
+        <v>3015252</v>
+      </c>
+      <c r="C146" s="6">
+        <v>6</v>
+      </c>
+      <c r="D146" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>3020958</v>
+      </c>
+      <c r="B147" s="6">
+        <v>3020958</v>
+      </c>
+      <c r="C147" s="6">
+        <v>6</v>
+      </c>
+      <c r="D147" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>3021204</v>
+      </c>
+      <c r="B148" s="6">
+        <v>3021204</v>
+      </c>
+      <c r="C148" s="6">
+        <v>6</v>
+      </c>
+      <c r="D148" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>3021970</v>
+      </c>
+      <c r="B149" s="6">
+        <v>3021970</v>
+      </c>
+      <c r="C149" s="6">
+        <v>6</v>
+      </c>
+      <c r="D149" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>3022191</v>
+      </c>
+      <c r="B150" s="6">
+        <v>3022191</v>
+      </c>
+      <c r="C150" s="6">
+        <v>6</v>
+      </c>
+      <c r="D150" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>3022206</v>
+      </c>
+      <c r="B151" s="6">
+        <v>3022206</v>
+      </c>
+      <c r="C151" s="6">
+        <v>6</v>
+      </c>
+      <c r="D151" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>3022389</v>
+      </c>
+      <c r="B152" s="6">
+        <v>3022389</v>
+      </c>
+      <c r="C152" s="6">
+        <v>6</v>
+      </c>
+      <c r="D152" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="6">
+        <v>3023114</v>
+      </c>
+      <c r="B153" s="6">
+        <v>3023114</v>
+      </c>
+      <c r="C153" s="6">
+        <v>6</v>
+      </c>
+      <c r="D153" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="6">
+        <v>3023115</v>
+      </c>
+      <c r="B154" s="6">
+        <v>3023115</v>
+      </c>
+      <c r="C154" s="6">
+        <v>6</v>
+      </c>
+      <c r="D154" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>3023414</v>
+      </c>
+      <c r="B155" s="6">
+        <v>3023414</v>
+      </c>
+      <c r="C155" s="6">
+        <v>6</v>
+      </c>
+      <c r="D155" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>3023812</v>
+      </c>
+      <c r="B156" s="6">
+        <v>3023812</v>
+      </c>
+      <c r="C156" s="6">
+        <v>6</v>
+      </c>
+      <c r="D156" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="6">
+        <v>3023813</v>
+      </c>
+      <c r="B157" s="6">
+        <v>3023813</v>
+      </c>
+      <c r="C157" s="6">
+        <v>6</v>
+      </c>
+      <c r="D157" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>3023814</v>
+      </c>
+      <c r="B158" s="6">
+        <v>3023814</v>
+      </c>
+      <c r="C158" s="6">
+        <v>6</v>
+      </c>
+      <c r="D158" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="6">
+        <v>3023815</v>
+      </c>
+      <c r="B159" s="6">
+        <v>3023815</v>
+      </c>
+      <c r="C159" s="6">
+        <v>6</v>
+      </c>
+      <c r="D159" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="6">
+        <v>3023818</v>
+      </c>
+      <c r="B160" s="6">
+        <v>3023818</v>
+      </c>
+      <c r="C160" s="6">
+        <v>6</v>
+      </c>
+      <c r="D160" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="6">
+        <v>3023841</v>
+      </c>
+      <c r="B161" s="6">
+        <v>3023841</v>
+      </c>
+      <c r="C161" s="6">
+        <v>6</v>
+      </c>
+      <c r="D161" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="6">
+        <v>3023847</v>
+      </c>
+      <c r="B162" s="6">
+        <v>3023847</v>
+      </c>
+      <c r="C162" s="6">
+        <v>6</v>
+      </c>
+      <c r="D162" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="6">
+        <v>3023857</v>
+      </c>
+      <c r="B163" s="6">
+        <v>3023857</v>
+      </c>
+      <c r="C163" s="6">
+        <v>6</v>
+      </c>
+      <c r="D163" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="6">
+        <v>3023858</v>
+      </c>
+      <c r="B164" s="6">
+        <v>3023858</v>
+      </c>
+      <c r="C164" s="6">
+        <v>6</v>
+      </c>
+      <c r="D164" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="6">
+        <v>3023861</v>
+      </c>
+      <c r="B165" s="6">
+        <v>3023861</v>
+      </c>
+      <c r="C165" s="6">
+        <v>6</v>
+      </c>
+      <c r="D165" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="6">
+        <v>3023870</v>
+      </c>
+      <c r="B166" s="6">
+        <v>3023870</v>
+      </c>
+      <c r="C166" s="6">
+        <v>6</v>
+      </c>
+      <c r="D166" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="6">
+        <v>3023921</v>
+      </c>
+      <c r="B167" s="6">
+        <v>3023921</v>
+      </c>
+      <c r="C167" s="6">
+        <v>6</v>
+      </c>
+      <c r="D167" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="6">
+        <v>3025188</v>
+      </c>
+      <c r="B168" s="6">
+        <v>3025188</v>
+      </c>
+      <c r="C168" s="6">
+        <v>6</v>
+      </c>
+      <c r="D168" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="6">
+        <v>3025234</v>
+      </c>
+      <c r="B169" s="6">
+        <v>3025234</v>
+      </c>
+      <c r="C169" s="6">
+        <v>6</v>
+      </c>
+      <c r="D169" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="6">
+        <v>3025276</v>
+      </c>
+      <c r="B170" s="6">
+        <v>3025276</v>
+      </c>
+      <c r="C170" s="6">
+        <v>6</v>
+      </c>
+      <c r="D170" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="6">
+        <v>3026113</v>
+      </c>
+      <c r="B171" s="6">
+        <v>3026113</v>
+      </c>
+      <c r="C171" s="6">
+        <v>6</v>
+      </c>
+      <c r="D171" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="6">
+        <v>3027576</v>
+      </c>
+      <c r="B172" s="6">
+        <v>3027576</v>
+      </c>
+      <c r="C172" s="6">
+        <v>6</v>
+      </c>
+      <c r="D172" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="6">
+        <v>3028794</v>
+      </c>
+      <c r="B173" s="6">
+        <v>3028794</v>
+      </c>
+      <c r="C173" s="6">
+        <v>6</v>
+      </c>
+      <c r="D173" s="9">
+        <v>46296.274312303241</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>